--- a/03_Outputs/all/01_TablasDescriptivas/idx12_salud.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx12_salud.xlsx
@@ -440,7 +440,7 @@
         <v>125</v>
       </c>
       <c r="C4">
-        <v>-363.4762135039615</v>
+        <v>-363.4762135039616</v>
       </c>
       <c r="D4">
         <v>1248.59996013325</v>
